--- a/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/group_reports/global_ui_summary.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/Feature_Importance/group_reports/global_ui_summary.xlsx
@@ -492,30 +492,30 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.166754478221572</v>
+        <v>0.154302547196298</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neuroticism, Openness, Conscientiousness</t>
+          <t>Neuroticism, Openness, Extraversion</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.1668, 0.1505, 0.1386</t>
+          <t>0.1543, 0.1529, 0.1404</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>primary_device, Neuroticism, current_mood</t>
+          <t>primary_device, Neuroticism, primary_persona</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0483, 0.0418, 0.0311</t>
+          <t>0.0381, 0.0299, 0.0282</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.04828259122900901</v>
+        <v>0.03809923856570584</v>
       </c>
     </row>
     <row r="3">
@@ -535,30 +535,30 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1750392083298654</v>
+        <v>0.156376594392571</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neuroticism, Extraversion, Agreeableness</t>
+          <t>Neuroticism, Agreeableness, Extraversion</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.1750, 0.1392, 0.1336</t>
+          <t>0.1564, 0.1440, 0.1414</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>current_mood, primary_persona, Extraversion</t>
+          <t>current_mood, Conscientiousness, Neuroticism</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0462, 0.0355, 0.0321</t>
+          <t>0.0276, 0.0261, 0.0249</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.04615599483440821</v>
+        <v>0.02755243525333835</v>
       </c>
     </row>
     <row r="4">
@@ -574,34 +574,34 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1615434309580455</v>
+        <v>0.147515215313564</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>primary_persona, Neuroticism, current_mood</t>
+          <t>Neuroticism, primary_persona, Conscientiousness</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.1615, 0.1456, 0.1414</t>
+          <t>0.1475, 0.1452, 0.1419</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>primary_persona, Agreeableness, Neuroticism</t>
+          <t>Neuroticism, Openness, Extraversion</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0297, 0.0236, 0.0201</t>
+          <t>0.0301, 0.0238, 0.0220</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.0297348840435253</v>
+        <v>0.03011478526552338</v>
       </c>
     </row>
     <row r="5">
@@ -617,34 +617,34 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Agreeableness</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1469942778243226</v>
+        <v>0.1456517975149239</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>current_mood, Openness, Conscientiousness</t>
+          <t>Agreeableness, Neuroticism, current_mood</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.1470, 0.1450, 0.1422</t>
+          <t>0.1457, 0.1423, 0.1419</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Openness, Neuroticism, current_mood</t>
+          <t>Neuroticism, primary_persona, Agreeableness</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0274, 0.0197, 0.0191</t>
+          <t>0.0205, 0.0205, 0.0198</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.02736537406851321</v>
+        <v>0.02052478693461994</v>
       </c>
     </row>
     <row r="6">
@@ -664,30 +664,30 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1539018391354902</v>
+        <v>0.1644723132958532</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, primary_persona</t>
+          <t>Neuroticism, primary_persona, Conscientiousness</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.1539, 0.1407, 0.1361</t>
+          <t>0.1645, 0.1426, 0.1349</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>current_mood, Neuroticism, Extraversion</t>
+          <t>Agreeableness, Neuroticism, Extraversion</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0483, 0.0318, 0.0272</t>
+          <t>0.0356, 0.0295, 0.0256</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.04828990137877086</v>
+        <v>0.03562855577852648</v>
       </c>
     </row>
     <row r="7">
@@ -703,34 +703,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>current_mood</t>
+          <t>Conscientiousness</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1507784783512724</v>
+        <v>0.1582355616342049</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Conscientiousness, Neuroticism, Openness</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.1582, 0.1499, 0.1376</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>current_mood, Neuroticism, Extraversion</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.1508, 0.1506, 0.1440</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Openness, Neuroticism, Conscientiousness</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0339, 0.0300, 0.0261</t>
+          <t>0.0382, 0.0323, 0.0305</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.03388854266615276</v>
+        <v>0.0382447927828469</v>
       </c>
     </row>
     <row r="8">
@@ -750,30 +750,30 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.1666568725148211</v>
+        <v>0.151966046643596</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, Extraversion</t>
+          <t>Neuroticism, Openness, Conscientiousness</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.1667, 0.1406, 0.1381</t>
+          <t>0.1520, 0.1427, 0.1397</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Agreeableness, Openness, current_mood</t>
+          <t>Agreeableness, Extraversion, Neuroticism</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0250, 0.0244, 0.0219</t>
+          <t>0.0229, 0.0229, 0.0220</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.02504461504999842</v>
+        <v>0.02293622100741881</v>
       </c>
     </row>
     <row r="9">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1608969971318128</v>
+        <v>0.1653523498251288</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.1609, 0.1453, 0.1421</t>
+          <t>0.1654, 0.1465, 0.1443</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>current_mood, Openness, primary_device</t>
+          <t>primary_device, Openness, Neuroticism</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0408, 0.0405, 0.0306</t>
+          <t>0.0344, 0.0311, 0.0282</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.04078750777312464</v>
+        <v>0.03436380317597383</v>
       </c>
     </row>
     <row r="10">
@@ -836,30 +836,30 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.1540470577757507</v>
+        <v>0.1559057778329406</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neuroticism, Agreeableness, Extraversion</t>
+          <t>Neuroticism, Conscientiousness, primary_persona</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.1540, 0.1435, 0.1403</t>
+          <t>0.1559, 0.1455, 0.1407</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neuroticism, primary_persona, current_mood</t>
+          <t>Neuroticism, current_mood, Agreeableness</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0406, 0.0362, 0.0311</t>
+          <t>0.0443, 0.0345, 0.0309</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.04055553676141661</v>
+        <v>0.04434580723534823</v>
       </c>
     </row>
     <row r="11">
@@ -879,30 +879,30 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.1605640408199236</v>
+        <v>0.151058511953328</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, primary_persona</t>
+          <t>Neuroticism, primary_persona, Conscientiousness</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.1606, 0.1469, 0.1468</t>
+          <t>0.1511, 0.1466, 0.1448</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neuroticism, Extraversion, primary_device</t>
+          <t>Neuroticism, primary_persona, Agreeableness</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0315, 0.0252, 0.0230</t>
+          <t>0.0376, 0.0305, 0.0258</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.03152006716729635</v>
+        <v>0.03758177776032348</v>
       </c>
     </row>
     <row r="12">
@@ -922,30 +922,30 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1541881133878216</v>
+        <v>0.1452802570235586</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neuroticism, primary_persona, Conscientiousness</t>
+          <t>Neuroticism, Openness, Extraversion</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.1542, 0.1436, 0.1400</t>
+          <t>0.1453, 0.1414, 0.1364</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>primary_device, Neuroticism, current_mood</t>
+          <t>current_mood, primary_device, Agreeableness</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0320, 0.0309, 0.0304</t>
+          <t>0.0356, 0.0340, 0.0320</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.03197838174348877</v>
+        <v>0.03563454222560034</v>
       </c>
     </row>
     <row r="13">
@@ -965,30 +965,30 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.1724525874473294</v>
+        <v>0.1645700749107897</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neuroticism, Conscientiousness, primary_persona</t>
+          <t>Neuroticism, Conscientiousness, Agreeableness</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.1725, 0.1614, 0.1333</t>
+          <t>0.1646, 0.1485, 0.1443</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Extraversion, current_mood, primary_device</t>
+          <t>primary_persona, Extraversion, current_mood</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.0310, 0.0303, 0.0247</t>
+          <t>0.0313, 0.0292, 0.0288</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.03097613547193547</v>
+        <v>0.03128778135807331</v>
       </c>
     </row>
     <row r="14">
@@ -1008,30 +1008,30 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.1586690174594589</v>
+        <v>0.149965430738608</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>primary_persona, Extraversion, Conscientiousness</t>
+          <t>primary_persona, Neuroticism, Agreeableness</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.1587, 0.1409, 0.1403</t>
+          <t>0.1500, 0.1407, 0.1368</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Agreeableness, primary_persona, Openness</t>
+          <t>primary_persona, current_mood, Conscientiousness</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0233, 0.0205, 0.0196</t>
+          <t>0.0200, 0.0182, 0.0181</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.02330734089617804</v>
+        <v>0.01998120909333736</v>
       </c>
     </row>
     <row r="15">
@@ -1047,34 +1047,34 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>primary_persona</t>
+          <t>Neuroticism</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1540095354726442</v>
+        <v>0.1488443327461026</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>primary_persona, Neuroticism, Agreeableness</t>
+          <t>Neuroticism, Agreeableness, Openness</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.1540, 0.1496, 0.1384</t>
+          <t>0.1488, 0.1469, 0.1428</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>primary_persona, Openness, Neuroticism</t>
+          <t>Conscientiousness, primary_device, Agreeableness</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0410, 0.0343, 0.0338</t>
+          <t>0.0349, 0.0343, 0.0324</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.0409993870133311</v>
+        <v>0.03490515958752668</v>
       </c>
     </row>
   </sheetData>
